--- a/tests/workbooktests/workbooks/test_termstructures.xlsx
+++ b/tests/workbooktests/workbooks/test_termstructures.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kerst\Desktop\FRAME\Pricing Software\Quantlib\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B041EF9C-348B-4751-AFDB-4AF10402FB6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C66E6B1A-0AC4-4B4F-ACFE-E480FB552C76}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{AB19F68A-3F3A-4039-9EC4-FD0D0D1E9554}"/>
   </bookViews>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -39,30 +28,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>ReferenceDate</t>
   </si>
@@ -88,9 +55,6 @@
     <t>Annual</t>
   </si>
   <si>
-    <t>Calendar</t>
-  </si>
-  <si>
     <t>qlFlatForward</t>
   </si>
   <si>
@@ -125,9 +89,6 @@
   </si>
   <si>
     <t>qlTermStructureAllowsExtrapolation</t>
-  </si>
-  <si>
-    <t>Target</t>
   </si>
   <si>
     <t>qlYieldTermStructureDiscount</t>
@@ -170,7 +131,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,7 +174,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -545,14 +506,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8510F9D-4D9E-4CE9-B99E-C913C431EFF3}">
-  <dimension ref="B2:C34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:C33"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="2" max="2" width="39.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -560,7 +521,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -568,7 +529,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3">
       <c r="B4" t="s">
         <v>2</v>
       </c>
@@ -576,7 +537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3">
       <c r="B5" t="s">
         <v>4</v>
       </c>
@@ -584,7 +545,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3">
       <c r="B6" t="s">
         <v>6</v>
       </c>
@@ -592,210 +553,202 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+    <row r="8" spans="2:3">
+      <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="e" cm="1">
-        <f t="array" aca="1" ref="C9" ca="1">_xll.qlFlatForward(C2,C3,C4,C5,C6,C7)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C8" t="str">
+        <f>_xll.qlFlatForward(C2,C3,C4,C5,C6)</f>
+        <v>欣[test_termstructures.xlsx]YieldTermStructure!R8C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3">
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1">
+        <f>C2+365</f>
+        <v>46023</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
       <c r="B11" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="1">
-        <f>C2+365</f>
-        <v>46023</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+        <f>C10+365</f>
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3">
+      <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="array" ref="C13">_xll.qlTermStructureDayCounter(C8)</f>
+        <v>Actual/365 (Fixed)</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1">
-        <f>C11+365</f>
-        <v>46388</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" t="e" cm="1">
-        <f t="array" aca="1" ref="C14" ca="1">_xll.qlTermStructureDayCounter(C9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C14">
+        <f t="array" ref="C14">_xll.qlTermStructureTimeFromReference(C8,C10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
       <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" t="e" cm="1">
-        <f t="array" aca="1" ref="C15" ca="1">_xll.qlTermStructureTimeFromReference(C9,C11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <f t="array" ref="C15">FIND("RuntimeError: RuntimeError: no calendar implementation provided", _xll.qlTermStructureCalendar(C8))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3">
       <c r="B16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="e" cm="1">
-        <f t="array" aca="1" ref="C16" ca="1">FIND("RuntimeError: RuntimeError: no calendar implementation provided", _xll.qlTermStructureCalendar(C9))</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C16" s="1">
+        <f t="array" ref="C16">_xll.qlTermStructureReferenceDate(C8)</f>
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
       <c r="B17" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C17" ca="1">_xll.qlTermStructureReferenceDate(C9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C17" s="1">
+        <f t="array" ref="C17">_xll.qlTermStructureMaxDate(C8)</f>
+        <v>109574</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
       <c r="B18" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C18" ca="1">_xll.qlTermStructureMaxDate(C9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C18" s="2">
+        <f t="array" ref="C18">_xll.qlTermStructureMaxTime(C8)</f>
+        <v>175.1123287671233</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
       <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="b">
+        <f t="array" ref="C19">_xll.qlTermStructureAllowsExtrapolation(C8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="B20" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="2" t="e" cm="1">
-        <f t="array" aca="1" ref="C19" ca="1">_xll.qlTermStructureMaxTime(C9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" t="e" cm="1">
-        <f t="array" aca="1" ref="C20" ca="1">_xll.qlTermStructureAllowsExtrapolation(C9)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C20" t="b">
+        <f t="array" ref="C20">_xll.qlTermStructureEnableExrapolation(C8,C19)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
       <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="b">
+        <f t="array" ref="C21">_xll.qlTermStructureAllowsExtrapolation(C8,C20)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" t="s">
         <v>18</v>
       </c>
-      <c r="C21" t="e" cm="1">
-        <f t="array" aca="1" ref="C21" ca="1">_xll.qlTermStructureEnableExrapolation(C9,C20)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
-        <v>20</v>
-      </c>
-      <c r="C22" t="e" cm="1">
-        <f t="array" aca="1" ref="C22" ca="1">_xll.qlTermStructureAllowsExtrapolation(C9,C21)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C22" t="b">
+        <f t="array" ref="C22">_xll.qlTermStructureDisableExrapolation(C8,C21)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
       <c r="B23" t="s">
         <v>19</v>
       </c>
-      <c r="C23" t="e" cm="1">
-        <f t="array" aca="1" ref="C23" ca="1">_xll.qlTermStructureDisableExrapolation(C9,C22)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+      <c r="C23" t="b">
+        <f t="array" ref="C23">_xll.qlTermStructureAllowsExtrapolation(C8,C22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3">
+      <c r="B25" t="s">
         <v>20</v>
       </c>
-      <c r="C24" t="e" cm="1">
-        <f t="array" aca="1" ref="C24" ca="1">_xll.qlTermStructureAllowsExtrapolation(C9,C23)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C25">
+        <f t="array" ref="C25">_xll.qlYieldTermStructureDiscount(C8,C10)</f>
+        <v>0.970873786407767</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
       <c r="B26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C26">
+        <f t="array" ref="C26">_xll.qlYieldTermStructureDiscountFromTime(C8,C14)</f>
+        <v>0.970873786407767</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3">
+      <c r="B27" t="s">
         <v>22</v>
       </c>
-      <c r="C26" t="e" cm="1">
-        <f t="array" aca="1" ref="C26" ca="1">_xll.qlYieldTermStructureDiscount(C9,C11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
+      <c r="C27">
+        <f t="array" ref="C27">_xll.qlYieldTermStructureZeroRate(C8,C10,C4,C5,C6)</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" t="s">
         <v>23</v>
       </c>
-      <c r="C27" t="e" cm="1">
-        <f t="array" aca="1" ref="C27" ca="1">_xll.qlYieldTermStructureDiscountFromTime(C9,C15)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B28" t="s">
+      <c r="C28">
+        <f t="array" ref="C28">_xll.qlYieldTermStructureZeroRateFromTime(C8,C14,C5,C6)</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" t="s">
         <v>24</v>
       </c>
-      <c r="C28" t="e" cm="1">
-        <f t="array" aca="1" ref="C28" ca="1">_xll.qlYieldTermStructureZeroRate(C9,C11,C4,C5,C6)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B29" t="s">
+      <c r="C29">
+        <f t="array" ref="C29">_xll.qlYieldTermStructureForwardRate(C8,C10,C11,C4,C5,C6)</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3">
+      <c r="B30" t="s">
         <v>25</v>
       </c>
-      <c r="C29" t="e" cm="1">
-        <f t="array" aca="1" ref="C29" ca="1">_xll.qlYieldTermStructureZeroRateFromTime(C9,C15,C5,C6)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
+      <c r="C30">
+        <f t="array" ref="C30">_xll.qlYieldTermStructureForwardRateFromTime(C8,C14,C14,C5,C6)</f>
+        <v>2.9999999998685745E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3">
+      <c r="B32" t="s">
         <v>26</v>
       </c>
-      <c r="C30" t="e" cm="1">
-        <f t="array" aca="1" ref="C30" ca="1">_xll.qlYieldTermStructureForwardRate(C9,C11,C12,C4,C5,C6)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" t="e" cm="1">
-        <f t="array" aca="1" ref="C31" ca="1">_xll.qlYieldTermStructureForwardRateFromTime(C9,C15,C15,C5,C6)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C32" t="str">
+        <f>_xll.qlImpliedTermStructure(C8,C10)</f>
+        <v>欣[test_termstructures.xlsx]YieldTermStructure!R32C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3">
       <c r="B33" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" t="e" cm="1">
-        <f t="array" aca="1" ref="C33" ca="1">_xll.qlImpliedTermStructure(C9,C11)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" t="e" cm="1">
-        <f t="array" aca="1" ref="C34" ca="1">_xll.qlYieldTermStructureDiscount(C33,C11)</f>
-        <v>#VALUE!</v>
+        <v>20</v>
+      </c>
+      <c r="C33">
+        <f t="array" ref="C33">_xll.qlYieldTermStructureDiscount(C32,C10)</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -805,14 +758,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{497B766F-DC5A-4DE8-A88C-90956781BACE}">
-  <dimension ref="B2:C24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:C23"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" customWidth="1"/>
+    <col min="2" max="2" width="26.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -820,7 +773,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -828,15 +781,15 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>0.01</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:3">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -844,7 +797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:3">
       <c r="B6" t="s">
         <v>4</v>
       </c>
@@ -852,7 +805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:3">
       <c r="B7" t="s">
         <v>6</v>
       </c>
@@ -860,102 +813,94 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+    <row r="9" spans="2:3">
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="e" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_xll.qlFlatForward(C2,C3,C5,C6,C7,C8)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C9" t="str">
+        <f>_xll.qlFlatForward(C2,C3,C5,C6,C7)</f>
+        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R9C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3">
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="array" ref="C11">_xll.qlZeroSpreadedTermStructure(C9,C4,C6,C7,C5)</f>
+        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R11C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3">
       <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12">
+        <f t="array" ref="C12">_xll.qlYieldTermStructureZeroRate(C11,$C$2+365,$C$5,$C$6,$C$7)</f>
+        <v>4.0000000000000036E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3">
+      <c r="B14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="array" ref="C14">_xll.qlForwardSpreadedTermStructure(C9,C4)</f>
+        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R14C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3">
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15">
+        <f t="array" ref="C15">_xll.qlYieldTermStructureZeroRate(C14,C2+365,C5,C6,C7)</f>
+        <v>4.0351672096692992E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="C12" t="e" cm="1">
-        <f t="array" aca="1" ref="C12" ca="1">_xll.qlZeroSpreadedTermStructure(C10,C4,C6,C7,C5)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="e" cm="1">
-        <f t="array" aca="1" ref="C13" ca="1">_xll.qlYieldTermStructureZeroRate(C12,$C$2+365,$C$5,$C$6,$C$7)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="C17" t="str">
+        <f>_xll.qlFlatForward(C2,C4,C5,C6,C7)</f>
+        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R17C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3">
+      <c r="B19" t="s">
         <v>31</v>
       </c>
-      <c r="C15" t="e" cm="1">
-        <f t="array" aca="1" ref="C15" ca="1">_xll.qlForwardSpreadedTermStructure(C10,C4)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="e" cm="1">
-        <f t="array" aca="1" ref="C16" ca="1">_xll.qlYieldTermStructureZeroRate(C15,C2+365,C5,C6,C7)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" t="e" cm="1">
-        <f t="array" aca="1" ref="C18" ca="1">_xll.qlFlatForward(C2,C4,C5,C6,C7,C8)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="C19" t="str">
+        <f t="array" ref="C19">_xll.qlCompositeZeroYieldStructure(C9,C17,"+")</f>
+        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R19C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
       <c r="B20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" t="e" cm="1">
-        <f t="array" aca="1" ref="C20" ca="1">_xll.qlCompositeZeroYieldStructure(C10,C18,"+")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" t="e" cm="1">
-        <f t="array" aca="1" ref="C21" ca="1">_xll.qlYieldTermStructureZeroRate(C20,$C$2+365,$C$5,$C$6,$C$7)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="C20">
+        <f t="array" ref="C20">_xll.qlYieldTermStructureZeroRate(C19,$C$2+365,$C$5,$C$6,$C$7)</f>
+        <v>4.0300000000000002E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3">
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="array" ref="C22">_xll.qlCompositeZeroYieldStructure(C9,C17,"-")</f>
+        <v>欣[test_termstructures.xlsx]Spreaded YieldTermStructures!R22C3YieldTermStructureHandle,A</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3">
       <c r="B23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" t="e" cm="1">
-        <f t="array" aca="1" ref="C23" ca="1">_xll.qlCompositeZeroYieldStructure(C10,C18,"-")</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" t="e" cm="1">
-        <f t="array" aca="1" ref="C24" ca="1">_xll.qlYieldTermStructureZeroRate(C23,$C$2+365,$C$5,$C$6,$C$7)</f>
-        <v>#VALUE!</v>
+        <v>22</v>
+      </c>
+      <c r="C23">
+        <f t="array" ref="C23">_xll.qlYieldTermStructureZeroRate(C22,$C$2+365,$C$5,$C$6,$C$7)</f>
+        <v>1.980198019801982E-2</v>
       </c>
     </row>
   </sheetData>
